--- a/source_data/supplementary_tables/Supplementary_Table_1.xlsx
+++ b/source_data/supplementary_tables/Supplementary_Table_1.xlsx
@@ -425,28 +425,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R267"/>
+  <dimension ref="A1:R257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="31" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="44" customWidth="1" min="15" max="15"/>
-    <col width="44" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -581,6 +561,16 @@
           <t>basal cytokeratin</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +613,16 @@
           <t>luminal cytokeratin; CK5/CK7 co-expression proxy</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -665,6 +665,16 @@
           <t>epithelial/luminal cytokeratin</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -707,6 +717,16 @@
           <t>stem/progenitor-like marker</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -749,6 +769,16 @@
           <t>stem/plasticity transcription factor</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -791,6 +821,16 @@
           <t>basoluminal-associated from supplement extraction</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -833,6 +873,16 @@
           <t>basal/TNBC epithelial marker</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -875,6 +925,16 @@
           <t>stem/EMT-associated marker</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -917,6 +977,16 @@
           <t>plasticity pathway</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -959,6 +1029,16 @@
           <t>mast marker</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1001,6 +1081,16 @@
           <t>mast marker</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1043,6 +1133,16 @@
           <t>mast marker</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1085,6 +1185,16 @@
           <t>FCER1 pathway mast/basophil marker</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1127,6 +1237,16 @@
           <t>mast marker</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1169,6 +1289,16 @@
           <t>from TNBC supplement markers</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1211,6 +1341,16 @@
           <t>mast lineage TF</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1253,6 +1393,16 @@
           <t>Tfh/TLS chemokine</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1295,6 +1445,16 @@
           <t>Tfh marker</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1337,6 +1497,16 @@
           <t>CD4_Tfh-DUSP4 marker</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1379,6 +1549,16 @@
           <t>CD4_Tfh-IL6ST marker</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1421,6 +1601,16 @@
           <t>activation/exhaustion marker; interpret with cell type</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1463,6 +1653,16 @@
           <t>checkpoint; interpret with cell type</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1505,6 +1705,16 @@
           <t>Tfh/B cell help</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1547,6 +1757,16 @@
           <t>Tfh-associated</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1589,6 +1809,16 @@
           <t>Tfh transcription factor</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1631,6 +1861,16 @@
           <t>Tfh-associated</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1673,6 +1913,16 @@
           <t>B cell/TLS marker</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1715,6 +1965,16 @@
           <t>B cell/TLS marker</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1757,6 +2017,16 @@
           <t>B cell/TLS marker</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1799,6 +2069,16 @@
           <t>CD8_Tsem-EOMES marker</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1841,6 +2121,16 @@
           <t>memory T marker</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1883,6 +2173,16 @@
           <t>stem-like memory T cell marker; verify expression in scRNA</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1925,6 +2225,16 @@
           <t>memory/effector marker</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1967,6 +2277,16 @@
           <t>chemokine receptor for CXCL9/10 axis</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2009,6 +2329,16 @@
           <t>memory/trafficking marker</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2051,6 +2381,16 @@
           <t>pro-inflammatory macrophage chemokine</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2093,6 +2433,16 @@
           <t>pro-inflammatory macrophage chemokine</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2135,6 +2485,16 @@
           <t>from Macro-CXCL9 marker extraction</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2177,6 +2537,16 @@
           <t>FOLR2 macrophage state</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2219,6 +2589,16 @@
           <t>HLA-II macrophage/APC marker</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2261,6 +2641,16 @@
           <t>HLA-II marker</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2303,6 +2693,16 @@
           <t>HLA-II chaperone</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2345,6 +2745,16 @@
           <t>macrophage marker</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2387,6 +2797,16 @@
           <t>macrophage transcription factor</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2429,6 +2849,16 @@
           <t>complement/macrophage marker</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2471,6 +2901,16 @@
           <t>cDC1 marker</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2513,6 +2953,16 @@
           <t>cDC1 marker</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2555,6 +3005,16 @@
           <t>cDC1 transcription factor</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2597,6 +3057,16 @@
           <t>mature DC/TLS marker</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2639,6 +3109,16 @@
           <t>trafficking marker</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2681,6 +3161,16 @@
           <t>TLS/CCR7 ligand</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2723,6 +3213,16 @@
           <t>HLA-II marker</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2765,6 +3265,16 @@
           <t>HLA-II marker</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2807,6 +3317,16 @@
           <t>HLA-II chaperone</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2849,6 +3369,16 @@
           <t>Macro-FN1 / matrix program</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2891,6 +3421,16 @@
           <t>TGF-beta-associated stromal/myeloid program</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2933,6 +3473,16 @@
           <t>myeloid chemokine</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2975,6 +3525,16 @@
           <t>Macro-RNASE1 marker</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3017,6 +3577,16 @@
           <t>M2-like macrophage marker</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3059,6 +3629,16 @@
           <t>Macro-MT1X marker</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3101,6 +3681,16 @@
           <t>stress program</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3143,6 +3733,16 @@
           <t>inflammatory suppressive myeloid marker</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3185,6 +3785,16 @@
           <t>inflammatory suppressive myeloid marker</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3227,6 +3837,16 @@
           <t>monocyte marker</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3269,6 +3889,16 @@
           <t>M2-like macrophage marker</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3311,6 +3941,16 @@
           <t>suppressive macrophage marker</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3353,6 +3993,16 @@
           <t>suppressive/tumor-associated macrophage marker</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3395,6 +4045,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3437,6 +4097,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3479,6 +4149,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3521,6 +4201,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3563,6 +4253,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3605,6 +4305,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3647,6 +4357,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3689,6 +4409,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3731,6 +4461,16 @@
           <t>proliferation control</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3773,6 +4513,16 @@
           <t>cytolytic activity control</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3815,6 +4565,16 @@
           <t>cytolytic activity control</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3857,6 +4617,16 @@
           <t>HLA-II control</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3899,6 +4669,16 @@
           <t>HLA-II control</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3941,6 +4721,16 @@
           <t>HLA-II control</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3983,6 +4773,16 @@
           <t>HLA-II control</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4025,6 +4825,16 @@
           <t>HLA-II control</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4067,6 +4877,16 @@
           <t>do not use as bulk tumor-cell marker without scRNA evidence</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4109,6 +4929,16 @@
           <t>TIM3 ligand; interpret cautiously</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4151,6 +4981,16 @@
           <t>TIM3-related ligand/cofactor</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4163,6 +5003,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4183,11 +5029,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4200,6 +5051,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4220,11 +5077,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4237,6 +5099,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4267,6 +5135,10 @@
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4279,6 +5151,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4299,11 +5177,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4316,6 +5199,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4346,6 +5235,10 @@
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4358,6 +5251,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4378,11 +5277,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4395,6 +5299,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4425,6 +5335,10 @@
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4437,6 +5351,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4457,11 +5377,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4474,6 +5399,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4494,11 +5425,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4511,6 +5447,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4531,11 +5473,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4548,6 +5495,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>GSE194040</t>
@@ -4568,11 +5521,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>results/GSE194040_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4585,6 +5543,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4605,11 +5569,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4622,6 +5591,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4652,6 +5627,10 @@
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4664,6 +5643,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4694,6 +5679,10 @@
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4706,6 +5695,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4726,11 +5721,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4743,6 +5743,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4773,6 +5779,10 @@
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4785,6 +5795,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4805,11 +5821,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4822,6 +5843,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4842,11 +5869,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4859,6 +5891,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4879,11 +5917,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4896,6 +5939,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4916,11 +5965,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4933,6 +5987,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -4963,6 +6023,10 @@
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4975,6 +6039,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>GSE25066_RMA</t>
@@ -5005,6 +6075,10 @@
           <t>results/GSE25066_RMA_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5017,6 +6091,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5037,11 +6117,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5054,6 +6139,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5074,11 +6165,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5091,6 +6187,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5111,11 +6213,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5128,6 +6235,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5148,11 +6261,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5165,6 +6283,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5185,11 +6309,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5202,6 +6331,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5222,11 +6357,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5239,6 +6379,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5269,6 +6415,10 @@
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5281,6 +6431,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5301,11 +6457,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5318,6 +6479,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5338,11 +6505,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5355,6 +6527,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5375,11 +6553,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5392,6 +6575,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>METABRIC</t>
@@ -5412,11 +6601,16 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr">
         <is>
           <t>results/METABRIC_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5429,6 +6623,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5449,6 +6649,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5464,6 +6665,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5476,6 +6679,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5516,6 +6725,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5528,6 +6739,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5568,6 +6785,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5580,6 +6799,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5600,6 +6825,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5615,6 +6841,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5627,6 +6855,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5667,6 +6901,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5679,6 +6915,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5699,6 +6941,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5714,6 +6957,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5726,6 +6971,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5746,6 +6997,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5761,6 +7013,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5773,6 +7027,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5793,6 +7053,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5808,6 +7069,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5820,6 +7083,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5840,6 +7109,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -5855,6 +7125,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5867,6 +7139,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5907,6 +7185,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5919,6 +7199,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -5959,6 +7245,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5971,6 +7259,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>GSE41998</t>
@@ -6011,6 +7305,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6023,6 +7319,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6043,6 +7345,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6058,6 +7361,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6070,6 +7375,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6110,6 +7421,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6122,6 +7435,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6162,6 +7481,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6174,6 +7495,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6194,6 +7521,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6209,6 +7537,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6221,6 +7551,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6261,6 +7597,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6273,6 +7611,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6293,6 +7637,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6308,6 +7653,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6320,6 +7667,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6340,6 +7693,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6355,6 +7709,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6367,6 +7723,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6387,6 +7749,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6402,6 +7765,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6414,6 +7779,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6434,6 +7805,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6449,6 +7821,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6461,6 +7835,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6501,6 +7881,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6513,6 +7895,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6553,6 +7941,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6565,6 +7955,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>GSE20194</t>
@@ -6605,6 +8001,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6617,6 +8015,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6637,6 +8041,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6657,6 +8062,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6669,6 +8075,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6689,6 +8101,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6709,6 +8122,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6721,6 +8135,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6766,6 +8186,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6778,6 +8199,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6798,6 +8225,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6818,6 +8246,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6830,6 +8259,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6875,6 +8310,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6887,6 +8323,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6907,6 +8349,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -6927,6 +8370,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6939,6 +8383,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -6984,6 +8434,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6996,6 +8447,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7016,6 +8473,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7036,6 +8494,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7048,6 +8507,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7093,6 +8558,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7105,6 +8571,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7150,6 +8622,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7162,6 +8635,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7182,6 +8661,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7202,6 +8682,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7214,6 +8695,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7259,6 +8746,7 @@
           <t>GPL1708</t>
         </is>
       </c>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7271,6 +8759,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7291,6 +8785,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7311,6 +8806,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7323,6 +8819,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7343,6 +8845,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7363,6 +8866,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7375,6 +8879,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7420,6 +8930,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7432,6 +8943,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7452,6 +8969,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7472,6 +8990,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -7484,6 +9003,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7529,6 +9054,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -7541,6 +9067,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7561,6 +9093,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7581,6 +9114,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -7593,6 +9127,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7638,6 +9178,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7650,6 +9191,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7670,6 +9217,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7690,6 +9238,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7702,6 +9251,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7747,6 +9302,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7759,6 +9315,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7779,6 +9341,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7799,6 +9362,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7811,6 +9375,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7831,6 +9401,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M167" t="inlineStr"/>
       <c r="N167" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7851,6 +9422,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7863,6 +9435,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>GSE22226</t>
@@ -7908,6 +9486,7 @@
           <t>GPL4133</t>
         </is>
       </c>
+      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7920,6 +9499,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -7940,6 +9525,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M169" t="inlineStr"/>
       <c r="N169" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -7955,6 +9541,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7967,6 +9555,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -7987,6 +9581,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8002,6 +9597,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8014,6 +9611,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8054,6 +9657,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8066,6 +9671,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8086,6 +9697,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8101,6 +9713,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8113,6 +9727,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8153,6 +9773,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8165,6 +9787,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8185,6 +9813,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8200,6 +9829,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8212,6 +9843,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8232,6 +9869,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8247,6 +9885,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8259,6 +9899,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8279,6 +9925,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8294,6 +9941,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8306,6 +9955,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8326,6 +9981,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8341,6 +9997,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8353,6 +10011,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8373,6 +10037,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8388,6 +10053,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8400,6 +10067,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8420,6 +10093,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8435,6 +10109,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8447,6 +10123,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>GSE32646</t>
@@ -8487,6 +10169,8 @@
           <t>symbol column: Gene symbol</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8499,6 +10183,12 @@
           <t>Basoluminal_plasticity</t>
         </is>
       </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8519,6 +10209,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8534,6 +10225,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -8546,6 +10239,12 @@
           <t>CD8_Tsem_memory</t>
         </is>
       </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8566,6 +10265,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8581,6 +10281,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -8593,6 +10295,12 @@
           <t>CXCL9_FOLR2_macrophage</t>
         </is>
       </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8613,6 +10321,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8628,6 +10337,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -8640,6 +10351,12 @@
           <t>Cytolytic</t>
         </is>
       </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8660,6 +10377,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8675,6 +10393,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -8687,6 +10407,12 @@
           <t>DC_HLA_antigen_presentation</t>
         </is>
       </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8707,6 +10433,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8722,6 +10449,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -8734,6 +10463,12 @@
           <t>HLAII</t>
         </is>
       </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8754,6 +10489,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8769,6 +10505,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -8781,6 +10519,12 @@
           <t>Mast_cell</t>
         </is>
       </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8801,6 +10545,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8816,6 +10561,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -8828,6 +10575,12 @@
           <t>Proliferation</t>
         </is>
       </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8848,6 +10601,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8863,6 +10617,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -8875,6 +10631,12 @@
           <t>Suppressive_myeloid</t>
         </is>
       </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8895,6 +10657,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8910,6 +10673,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8922,6 +10687,12 @@
           <t>Tfh_TLS_like</t>
         </is>
       </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8942,6 +10713,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -8957,6 +10729,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8969,6 +10743,12 @@
           <t>TIM3_cell_source_check</t>
         </is>
       </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -8989,6 +10769,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M191" t="inlineStr"/>
       <c r="N191" t="inlineStr">
         <is>
           <t>results/round4_external_signature_coverage.tsv</t>
@@ -9004,6 +10785,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9016,6 +10799,12 @@
           <t>APC_CXCL9_axis</t>
         </is>
       </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>GSE163882</t>
@@ -9056,6 +10845,8 @@
           <t>org.Hs.eg.db ENSEMBL-to-SYMBOL mapping</t>
         </is>
       </c>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9063,6 +10854,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9083,11 +10881,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
       <c r="R193" t="inlineStr">
         <is>
           <t>Basoluminal_plasticity</t>
@@ -9100,6 +10902,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9120,11 +10929,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M194" t="inlineStr"/>
       <c r="N194" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr">
         <is>
           <t>CD8_Tsem_memory</t>
@@ -9137,6 +10950,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9157,11 +10977,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
       <c r="R195" t="inlineStr">
         <is>
           <t>CXCL9_FOLR2_macrophage</t>
@@ -9174,6 +10998,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9194,11 +11025,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
       <c r="R196" t="inlineStr">
         <is>
           <t>Cytolytic</t>
@@ -9211,6 +11046,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9231,11 +11073,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
       <c r="R197" t="inlineStr">
         <is>
           <t>DC_HLA_antigen_presentation</t>
@@ -9248,6 +11094,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9268,11 +11121,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M198" t="inlineStr"/>
       <c r="N198" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
       <c r="R198" t="inlineStr">
         <is>
           <t>HLAII</t>
@@ -9285,6 +11142,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9305,11 +11169,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M199" t="inlineStr"/>
       <c r="N199" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
       <c r="R199" t="inlineStr">
         <is>
           <t>Mast_cell</t>
@@ -9322,6 +11190,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B200" t="inlineStr"/>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9342,11 +11217,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M200" t="inlineStr"/>
       <c r="N200" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr">
         <is>
           <t>Proliferation</t>
@@ -9359,6 +11238,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9379,11 +11265,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
       <c r="R201" t="inlineStr">
         <is>
           <t>Suppressive_myeloid</t>
@@ -9396,6 +11286,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9416,11 +11313,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M202" t="inlineStr"/>
       <c r="N202" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
       <c r="R202" t="inlineStr">
         <is>
           <t>Tfh_TLS_like</t>
@@ -9433,6 +11334,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B203" t="inlineStr"/>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9453,11 +11361,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
       <c r="R203" t="inlineStr">
         <is>
           <t>mast_marker</t>
@@ -9470,6 +11382,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9490,11 +11409,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr">
         <is>
           <t>tfh_tls_marker</t>
@@ -9507,6 +11430,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B205" t="inlineStr"/>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9527,11 +11457,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
       <c r="R205" t="inlineStr">
         <is>
           <t>cd8_tsem_marker</t>
@@ -9544,6 +11478,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B206" t="inlineStr"/>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9564,11 +11505,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
       <c r="R206" t="inlineStr">
         <is>
           <t>Basoluminal_plasticity</t>
@@ -9581,6 +11526,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9601,11 +11553,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M207" t="inlineStr"/>
       <c r="N207" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
       <c r="R207" t="inlineStr">
         <is>
           <t>CD8_Tsem_memory</t>
@@ -9618,6 +11574,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B208" t="inlineStr"/>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9638,11 +11601,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M208" t="inlineStr"/>
       <c r="N208" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr">
         <is>
           <t>CXCL9_FOLR2_macrophage</t>
@@ -9655,6 +11622,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9675,11 +11649,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
       <c r="R209" t="inlineStr">
         <is>
           <t>Cytolytic</t>
@@ -9692,6 +11670,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B210" t="inlineStr"/>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9712,11 +11697,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr">
         <is>
           <t>DC_HLA_antigen_presentation</t>
@@ -9729,6 +11718,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9749,11 +11745,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr">
         <is>
           <t>HLAII</t>
@@ -9766,6 +11766,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B212" t="inlineStr"/>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9786,11 +11793,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
       <c r="R212" t="inlineStr">
         <is>
           <t>Mast_cell</t>
@@ -9803,6 +11814,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B213" t="inlineStr"/>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9823,11 +11841,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M213" t="inlineStr"/>
       <c r="N213" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
       <c r="R213" t="inlineStr">
         <is>
           <t>Proliferation</t>
@@ -9840,6 +11862,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9860,11 +11889,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M214" t="inlineStr"/>
       <c r="N214" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
       <c r="R214" t="inlineStr">
         <is>
           <t>Suppressive_myeloid</t>
@@ -9877,6 +11910,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B215" t="inlineStr"/>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9897,11 +11937,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M215" t="inlineStr"/>
       <c r="N215" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
       <c r="R215" t="inlineStr">
         <is>
           <t>Tfh_TLS_like</t>
@@ -9914,6 +11958,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B216" t="inlineStr"/>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9934,11 +11985,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M216" t="inlineStr"/>
       <c r="N216" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
       <c r="R216" t="inlineStr">
         <is>
           <t>mast_marker</t>
@@ -9951,6 +12006,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B217" t="inlineStr"/>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -9971,11 +12033,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M217" t="inlineStr"/>
       <c r="N217" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
       <c r="R217" t="inlineStr">
         <is>
           <t>tfh_tls_marker</t>
@@ -9988,6 +12054,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10008,11 +12081,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
       <c r="R218" t="inlineStr">
         <is>
           <t>cd8_tsem_marker</t>
@@ -10025,6 +12102,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10045,11 +12129,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M219" t="inlineStr"/>
       <c r="N219" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr">
         <is>
           <t>Basoluminal_plasticity</t>
@@ -10062,6 +12150,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10082,11 +12177,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M220" t="inlineStr"/>
       <c r="N220" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
       <c r="R220" t="inlineStr">
         <is>
           <t>CD8_Tsem_memory</t>
@@ -10099,6 +12198,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10119,11 +12225,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
       <c r="R221" t="inlineStr">
         <is>
           <t>CXCL9_FOLR2_macrophage</t>
@@ -10136,6 +12246,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10156,11 +12273,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M222" t="inlineStr"/>
       <c r="N222" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
       <c r="R222" t="inlineStr">
         <is>
           <t>Cytolytic</t>
@@ -10173,6 +12294,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10193,11 +12321,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M223" t="inlineStr"/>
       <c r="N223" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr">
         <is>
           <t>DC_HLA_antigen_presentation</t>
@@ -10210,6 +12342,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10230,11 +12369,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M224" t="inlineStr"/>
       <c r="N224" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
       <c r="R224" t="inlineStr">
         <is>
           <t>HLAII</t>
@@ -10247,6 +12390,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10267,11 +12417,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M225" t="inlineStr"/>
       <c r="N225" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
       <c r="R225" t="inlineStr">
         <is>
           <t>Mast_cell</t>
@@ -10284,6 +12438,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10304,11 +12465,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M226" t="inlineStr"/>
       <c r="N226" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
       <c r="R226" t="inlineStr">
         <is>
           <t>Proliferation</t>
@@ -10321,6 +12486,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10341,11 +12513,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M227" t="inlineStr"/>
       <c r="N227" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
       <c r="R227" t="inlineStr">
         <is>
           <t>Suppressive_myeloid</t>
@@ -10358,6 +12534,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10378,11 +12561,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M228" t="inlineStr"/>
       <c r="N228" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
       <c r="R228" t="inlineStr">
         <is>
           <t>Tfh_TLS_like</t>
@@ -10395,6 +12582,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10415,11 +12609,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M229" t="inlineStr"/>
       <c r="N229" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
       <c r="R229" t="inlineStr">
         <is>
           <t>mast_marker</t>
@@ -10432,6 +12630,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10452,11 +12657,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M230" t="inlineStr"/>
       <c r="N230" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
       <c r="R230" t="inlineStr">
         <is>
           <t>tfh_tls_marker</t>
@@ -10469,6 +12678,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10489,11 +12705,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M231" t="inlineStr"/>
       <c r="N231" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr">
         <is>
           <t>cd8_tsem_marker</t>
@@ -10506,6 +12726,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10526,11 +12753,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M232" t="inlineStr"/>
       <c r="N232" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
       <c r="R232" t="inlineStr">
         <is>
           <t>Basoluminal_plasticity</t>
@@ -10543,6 +12774,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10563,11 +12801,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M233" t="inlineStr"/>
       <c r="N233" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
       <c r="R233" t="inlineStr">
         <is>
           <t>CD8_Tsem_memory</t>
@@ -10580,6 +12822,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10600,11 +12849,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M234" t="inlineStr"/>
       <c r="N234" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
       <c r="R234" t="inlineStr">
         <is>
           <t>CXCL9_FOLR2_macrophage</t>
@@ -10617,6 +12870,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10637,11 +12897,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M235" t="inlineStr"/>
       <c r="N235" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
       <c r="R235" t="inlineStr">
         <is>
           <t>Cytolytic</t>
@@ -10654,6 +12918,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10674,11 +12945,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M236" t="inlineStr"/>
       <c r="N236" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
       <c r="R236" t="inlineStr">
         <is>
           <t>DC_HLA_antigen_presentation</t>
@@ -10691,6 +12966,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10711,11 +12993,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M237" t="inlineStr"/>
       <c r="N237" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
       <c r="R237" t="inlineStr">
         <is>
           <t>HLAII</t>
@@ -10728,6 +13014,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10748,11 +13041,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M238" t="inlineStr"/>
       <c r="N238" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
       <c r="R238" t="inlineStr">
         <is>
           <t>Mast_cell</t>
@@ -10765,6 +13062,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10785,11 +13089,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M239" t="inlineStr"/>
       <c r="N239" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
       <c r="R239" t="inlineStr">
         <is>
           <t>Proliferation</t>
@@ -10802,6 +13110,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10822,11 +13137,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M240" t="inlineStr"/>
       <c r="N240" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
       <c r="R240" t="inlineStr">
         <is>
           <t>Suppressive_myeloid</t>
@@ -10839,6 +13158,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10859,11 +13185,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M241" t="inlineStr"/>
       <c r="N241" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
       <c r="R241" t="inlineStr">
         <is>
           <t>Tfh_TLS_like</t>
@@ -10876,6 +13206,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10896,11 +13233,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M242" t="inlineStr"/>
       <c r="N242" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
       <c r="R242" t="inlineStr">
         <is>
           <t>mast_marker</t>
@@ -10913,6 +13254,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10933,11 +13281,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M243" t="inlineStr"/>
       <c r="N243" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
       <c r="R243" t="inlineStr">
         <is>
           <t>tfh_tls_marker</t>
@@ -10950,6 +13302,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -10970,11 +13329,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M244" t="inlineStr"/>
       <c r="N244" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
       <c r="R244" t="inlineStr">
         <is>
           <t>cd8_tsem_marker</t>
@@ -10987,6 +13350,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11007,11 +13377,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
       <c r="R245" t="inlineStr">
         <is>
           <t>Basoluminal_plasticity</t>
@@ -11024,6 +13398,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11044,11 +13425,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M246" t="inlineStr"/>
       <c r="N246" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
       <c r="R246" t="inlineStr">
         <is>
           <t>CD8_Tsem_memory</t>
@@ -11061,6 +13446,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11081,11 +13473,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M247" t="inlineStr"/>
       <c r="N247" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
       <c r="R247" t="inlineStr">
         <is>
           <t>CXCL9_FOLR2_macrophage</t>
@@ -11098,6 +13494,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11118,11 +13521,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M248" t="inlineStr"/>
       <c r="N248" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
       <c r="R248" t="inlineStr">
         <is>
           <t>Cytolytic</t>
@@ -11135,6 +13542,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11165,6 +13579,9 @@
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
       <c r="R249" t="inlineStr">
         <is>
           <t>DC_HLA_antigen_presentation</t>
@@ -11177,6 +13594,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11197,11 +13621,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M250" t="inlineStr"/>
       <c r="N250" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
       <c r="R250" t="inlineStr">
         <is>
           <t>HLAII</t>
@@ -11214,6 +13642,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11244,6 +13679,9 @@
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
       <c r="R251" t="inlineStr">
         <is>
           <t>Mast_cell</t>
@@ -11256,6 +13694,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11276,11 +13721,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M252" t="inlineStr"/>
       <c r="N252" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
       <c r="R252" t="inlineStr">
         <is>
           <t>Proliferation</t>
@@ -11293,6 +13742,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B253" t="inlineStr"/>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11313,11 +13769,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
       <c r="R253" t="inlineStr">
         <is>
           <t>Suppressive_myeloid</t>
@@ -11330,6 +13790,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11350,11 +13817,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M254" t="inlineStr"/>
       <c r="N254" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
       <c r="R254" t="inlineStr">
         <is>
           <t>Tfh_TLS_like</t>
@@ -11367,6 +13838,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11397,6 +13875,9 @@
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
       <c r="R255" t="inlineStr">
         <is>
           <t>mast_marker</t>
@@ -11409,6 +13890,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11429,11 +13917,15 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
       <c r="R256" t="inlineStr">
         <is>
           <t>tfh_tls_marker</t>
@@ -11446,6 +13938,13 @@
           <t>cohort_signature_coverage</t>
         </is>
       </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>GSE266919</t>
@@ -11466,439 +13965,18 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M257" t="inlineStr"/>
       <c r="N257" t="inlineStr">
         <is>
           <t>results/GSE266919_subcluster_signature_coverage.tsv</t>
         </is>
       </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
       <c r="R257" t="inlineStr">
         <is>
           <t>cd8_tsem_marker</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Basoluminal_plasticity</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>CD8_Tsem_memory</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>CXCL9_FOLR2_macrophage</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J260" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr">
-        <is>
-          <t>CCL3L1</t>
-        </is>
-      </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>Cytolytic</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>DC_HLA_antigen_presentation</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>HLAII</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J263" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>Mast_cell</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J264" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Proliferation</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>Suppressive_myeloid</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>cohort_signature_coverage</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>Tfh_TLS_like</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Coverage adequate for lightweight cell-source scoring.</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
-        <is>
-          <t>GSE176078</t>
-        </is>
-      </c>
-      <c r="J267" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>results/GSE176078_scrna_signature_gene_coverage.tsv</t>
         </is>
       </c>
     </row>
